--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45163.60922423354</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>338.85</v>
+        <v>389.678</v>
       </c>
       <c r="E33" s="3" t="n"/>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="16" t="n">
-        <v>502.772</v>
+        <v>578.188</v>
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="16" t="n">
-        <v>629.9880000000001</v>
+        <v>724.486</v>
       </c>
       <c r="E35" s="3" t="n"/>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="16" t="n">
-        <v>758.442</v>
+        <v>872.208</v>
       </c>
       <c r="E36" s="3" t="n"/>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="16" t="n">
-        <v>829.403</v>
+        <v>953.813</v>
       </c>
       <c r="E37" s="3" t="n"/>
     </row>
@@ -1114,10 +1114,6 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -1127,17 +1123,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -1123,17 +1123,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1123,17 +1123,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/mi/SOPORTE BRACKET.xlsx
+++ b/LISTAS/mi/SOPORTE BRACKET.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45261.57776003047</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C33" s="29" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>389.678</v>
+        <v>596.46</v>
       </c>
       <c r="E33" s="3" t="n"/>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="16" t="n">
-        <v>578.188</v>
+        <v>885</v>
       </c>
       <c r="E34" s="3" t="n"/>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="16" t="n">
-        <v>724.486</v>
+        <v>1108.93</v>
       </c>
       <c r="E35" s="3" t="n"/>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="16" t="n">
-        <v>872.208</v>
+        <v>1335.04</v>
       </c>
       <c r="E36" s="3" t="n"/>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="16" t="n">
-        <v>953.813</v>
+        <v>1459.95</v>
       </c>
       <c r="E37" s="3" t="n"/>
     </row>
@@ -1114,6 +1114,10 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -1123,17 +1127,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
